--- a/data/demo/bestbuy_reviews_sentiment.xlsx
+++ b/data/demo/bestbuy_reviews_sentiment.xlsx
@@ -47,7 +47,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -57,7 +57,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -561,11 +561,11 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>-0.408</v>
+        <v>0</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.853</v>
+        <v>0.9</v>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>-0.209</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+        <v>-0.511</v>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>['Design (Pos)', 'Quality &amp; Durability (Pos)', 'Performance (Pos)', 'Display &amp; Sound (Neg)', 'Overall Satisfaction (Neg)']</t>
+          <t>['Design (Pos)', 'Quality &amp; Durability (Pos)', 'Performance (Pos)', 'Display &amp; Sound (Neg)', 'Overall Satisfaction (Neu)']</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -708,9 +708,9 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>-0.577</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
+        <v>-0.66</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -757,11 +757,11 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -806,16 +806,16 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
+        <v>-0.44</v>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>['Quality &amp; Durability (Neg)', 'Customer Service &amp; Delivery (Neg)']</t>
+          <t>['Quality &amp; Durability (Neu)', 'Customer Service &amp; Delivery (Neg)']</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
@@ -855,9 +855,9 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
+        <v>-0.844</v>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.535</v>
+        <v>0.784</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.632</v>
+        <v>0.556</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
@@ -1051,9 +1051,9 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>-0.229</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
+        <v>-0.5649999999999999</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.535</v>
+        <v>0.784</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.535</v>
+        <v>0.7</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.603</v>
+        <v>0.113</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.436</v>
+        <v>0.898</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -1296,9 +1296,9 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>-0.471</v>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+        <v>-0.709</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.516</v>
+        <v>0.772</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -1394,23 +1394,19 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>-0.196</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Negative</t>
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>['Ease of Use (Neu)', 'Performance (Neg)', 'Display &amp; Sound (Neg)']</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>High rating / negative text</t>
-        </is>
-      </c>
+          <t>['Ease of Use (Pos)', 'Performance (Neu)', 'Display &amp; Sound (Neu)']</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1447,9 +1443,9 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>-0.832</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
+        <v>-0.44</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -1496,7 +1492,7 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.302</v>
+        <v>0.431</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
@@ -1545,7 +1541,7 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.209</v>
+        <v>0.103</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -1554,7 +1550,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>['Design (Pos)', 'Quality &amp; Durability (Pos)', 'Ease of Use (Neg)', 'Performance (Pos)', 'Overall Satisfaction (Neg)']</t>
+          <t>['Design (Pos)', 'Quality &amp; Durability (Pos)', 'Ease of Use (Neg)', 'Performance (Pos)', 'Overall Satisfaction (Neu)']</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1598,7 +1594,7 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.832</v>
+        <v>0.848</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
@@ -1647,9 +1643,9 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>-0.832</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
+        <v>-0.44</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -1696,11 +1692,11 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>-0.213</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>Negative</t>
+        <v>0.09</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1745,7 +1741,7 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
@@ -1794,7 +1790,7 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1</v>
+        <v>0.917</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
@@ -1843,16 +1839,16 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>-1</v>
+        <v>-0.026</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>['Ease of Use (Neg)', 'Performance (Neg)', 'Display &amp; Sound (Neg)']</t>
+          <t>['Ease of Use (Neu)', 'Performance (Neu)', 'Display &amp; Sound (Neu)']</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -1892,7 +1888,7 @@
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.302</v>
+        <v>0.431</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
@@ -1941,7 +1937,7 @@
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
@@ -1990,11 +1986,11 @@
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>Neutral</t>
+        <v>0.202</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2039,9 +2035,9 @@
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>-0.436</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+        <v>-0.765</v>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -2088,7 +2084,7 @@
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.535</v>
+        <v>0.784</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
@@ -2137,7 +2133,7 @@
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
@@ -2186,7 +2182,7 @@
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
@@ -2235,7 +2231,7 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
@@ -2284,9 +2280,9 @@
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>-0.743</v>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
+        <v>-0.8</v>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -2333,7 +2329,7 @@
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
@@ -2382,16 +2378,16 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>-1</v>
+        <v>-0.026</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>['Ease of Use (Neg)', 'Performance (Neg)', 'Display &amp; Sound (Neg)']</t>
+          <t>['Ease of Use (Neu)', 'Performance (Neu)', 'Display &amp; Sound (Neu)']</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
@@ -2431,7 +2427,7 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>0.516</v>
+        <v>0.772</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -2480,16 +2476,16 @@
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>-0.928</v>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
+        <v>-0.509</v>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>['Ease of Use (Neg)', 'Performance (Neg)', 'Display &amp; Sound (Neg)', 'Connectivity (Neu)', 'Overall Satisfaction (Neg)']</t>
+          <t>['Ease of Use (Neu)', 'Performance (Neu)', 'Display &amp; Sound (Neu)', 'Connectivity (Neu)', 'Overall Satisfaction (Neg)']</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
@@ -2529,7 +2525,7 @@
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.784</v>
+        <v>0.896</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2574,7 @@
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.555</v>
+        <v>0.886</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
@@ -2627,7 +2623,7 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.555</v>
+        <v>0.886</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
@@ -2676,9 +2672,9 @@
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>-0.471</v>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
+        <v>-0.709</v>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -2725,7 +2721,7 @@
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0.832</v>
+        <v>0.848</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
@@ -2774,7 +2770,7 @@
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0.516</v>
+        <v>0.772</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
@@ -2823,7 +2819,7 @@
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
@@ -2872,7 +2868,7 @@
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.302</v>
+        <v>0.34</v>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
@@ -2921,7 +2917,7 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0.555</v>
+        <v>0.886</v>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
@@ -2970,7 +2966,7 @@
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>0.832</v>
+        <v>0.848</v>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
@@ -3019,16 +3015,16 @@
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>-0.905</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>['Quality &amp; Durability (Neg)']</t>
+          <t>['Quality &amp; Durability (Neu)']</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
@@ -3068,9 +3064,9 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>-0.832</v>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
+        <v>-0.44</v>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -3117,7 +3113,7 @@
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.302</v>
+        <v>0.34</v>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
@@ -3166,9 +3162,9 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>-0.471</v>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
+        <v>-0.709</v>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -3215,7 +3211,7 @@
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.183</v>
+        <v>0.383</v>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
@@ -3264,7 +3260,7 @@
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0.555</v>
+        <v>0.886</v>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
@@ -3313,7 +3309,7 @@
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0.302</v>
+        <v>0.34</v>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
@@ -3362,7 +3358,7 @@
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.302</v>
+        <v>0.34</v>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
@@ -3411,7 +3407,7 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.612</v>
+        <v>0.947</v>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
@@ -3460,16 +3456,16 @@
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>-0.905</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>['Quality &amp; Durability (Neg)']</t>
+          <t>['Quality &amp; Durability (Neu)']</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
@@ -3490,7 +3486,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3549,7 +3545,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3557,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3569,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>23.3</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3581,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3593,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>built-in word-list fallback (pip install vaderSentiment for better accuracy)</t>
+          <t>VADER</t>
         </is>
       </c>
     </row>
@@ -3665,16 +3661,16 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>38</v>
       </c>
       <c r="F2" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="3">
@@ -3687,16 +3683,16 @@
         <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="4">
@@ -3709,16 +3705,16 @@
         <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="5">
@@ -3753,16 +3749,16 @@
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>0.18</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="7">
@@ -3772,19 +3768,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>0.19</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="8">
